--- a/연구코드/aec/results/신촌/feature_selection_report.xlsx
+++ b/연구코드/aec/results/신촌/feature_selection_report.xlsx
@@ -10,7 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상관계수_전체" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상관계수_Top20" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIF_선택feature" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAMA_분포_성별" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIF_부분제거_비교" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAMA_분포_성별" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CT_스캐너_분포" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kVp_분포" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,29 +487,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.4966e-01</t>
+          <t>2.4430e-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.9851e-19</t>
+          <t>1.0629e-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.5726e-01</t>
+          <t>2.5064e-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.4355e-20</t>
+          <t>1.2475e-19</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.24966</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="3">
@@ -515,34 +518,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>min</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.4813e-01</t>
+          <t>2.4273e-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.3413e-19</t>
+          <t>1.7907e-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.5108e-01</t>
+          <t>2.3123e-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.2225e-19</t>
+          <t>7.2834e-17</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24813</v>
+        <v>0.24273</v>
       </c>
     </row>
     <row r="4">
@@ -551,34 +554,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.4697e-01</t>
+          <t>2.4228e-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.9386e-19</t>
+          <t>2.0812e-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.3674e-01</t>
+          <t>2.4467e-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.4235e-17</t>
+          <t>9.3993e-19</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24697</v>
+        <v>0.24228</v>
       </c>
     </row>
     <row r="5">
@@ -592,29 +595,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.4139e-01</t>
+          <t>2.3686e-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.1449e-18</t>
+          <t>1.2178e-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.3510e-01</t>
+          <t>2.2931e-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.4050e-17</t>
+          <t>1.3272e-16</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.24139</v>
+        <v>0.23686</v>
       </c>
     </row>
     <row r="6">
@@ -623,34 +626,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>AUC_normalized</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.3935e-01</t>
+          <t>2.3408e-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.1197e-18</t>
+          <t>2.9653e-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.3958e-01</t>
+          <t>2.2396e-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.6872e-18</t>
+          <t>6.8585e-16</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H6" t="n">
-        <v>0.23935</v>
+        <v>0.23408</v>
       </c>
     </row>
     <row r="7">
@@ -659,34 +662,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUC_normalized</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.3926e-01</t>
+          <t>2.3393e-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.2968e-18</t>
+          <t>3.1054e-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.3085e-01</t>
+          <t>2.2384e-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.1731e-17</t>
+          <t>7.1052e-16</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H7" t="n">
-        <v>0.23926</v>
+        <v>0.23393</v>
       </c>
     </row>
     <row r="8">
@@ -695,34 +698,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.3910e-01</t>
+          <t>2.3343e-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.6482e-18</t>
+          <t>3.6385e-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.3072e-01</t>
+          <t>2.3202e-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.5549e-17</t>
+          <t>5.6859e-17</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2391</v>
+        <v>0.23343</v>
       </c>
     </row>
     <row r="9">
@@ -736,29 +739,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.3284e-01</t>
+          <t>2.2908e-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.9057e-17</t>
+          <t>1.4244e-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.1505e-01</t>
+          <t>2.0905e-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.0596e-14</t>
+          <t>5.3505e-14</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H9" t="n">
-        <v>0.23284</v>
+        <v>0.22908</v>
       </c>
     </row>
     <row r="10">
@@ -772,29 +775,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.2811e-01</t>
+          <t>2.2395e-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.1466e-16</t>
+          <t>6.8832e-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.1821e-01</t>
+          <t>2.1194e-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.2205e-15</t>
+          <t>2.3563e-14</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H10" t="n">
-        <v>0.22811</v>
+        <v>0.22395</v>
       </c>
     </row>
     <row r="11">
@@ -808,29 +811,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.2113e-01</t>
+          <t>2.1758e-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.7811e-15</t>
+          <t>4.6045e-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.0606e-01</t>
+          <t>2.0004e-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.3509e-13</t>
+          <t>6.3992e-13</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H11" t="n">
-        <v>0.22113</v>
+        <v>0.21758</v>
       </c>
     </row>
     <row r="12">
@@ -839,34 +842,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.1937e-01</t>
+          <t>2.1490e-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0002e-15</t>
+          <t>1.0063e-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.0271e-01</t>
+          <t>1.9810e-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3.3778e-13</t>
+          <t>1.0739e-12</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H12" t="n">
-        <v>0.21937</v>
+        <v>0.2149</v>
       </c>
     </row>
     <row r="13">
@@ -875,34 +878,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>p95</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.1868e-01</t>
+          <t>2.1435e-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.6821e-15</t>
+          <t>1.1788e-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.0424e-01</t>
+          <t>1.9569e-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.2287e-13</t>
+          <t>2.0305e-12</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H13" t="n">
-        <v>0.21868</v>
+        <v>0.21435</v>
       </c>
     </row>
     <row r="14">
@@ -916,29 +919,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.1696e-01</t>
+          <t>2.1285e-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.0931e-15</t>
+          <t>1.8171e-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.0137e-01</t>
+          <t>1.9507e-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.8537e-13</t>
+          <t>2.3932e-12</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H14" t="n">
-        <v>0.21696</v>
+        <v>0.21285</v>
       </c>
     </row>
     <row r="15">
@@ -952,29 +955,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.0892e-01</t>
+          <t>2.0406e-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.0885e-14</t>
+          <t>2.1440e-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.2298e-01</t>
+          <t>2.1604e-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.0227e-15</t>
+          <t>7.2167e-15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H15" t="n">
-        <v>0.20892</v>
+        <v>0.20406</v>
       </c>
     </row>
     <row r="16">
@@ -988,29 +991,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.0849e-01</t>
+          <t>2.0380e-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.8648e-14</t>
+          <t>2.3007e-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.2891e-01</t>
+          <t>2.2181e-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.6781e-16</t>
+          <t>1.3105e-15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.20849</v>
+        <v>0.2038</v>
       </c>
     </row>
     <row r="17">
@@ -1024,29 +1027,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.0379e-01</t>
+          <t>1.9951e-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.5190e-13</t>
+          <t>7.3758e-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.2539e-01</t>
+          <t>2.1835e-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4.9412e-16</t>
+          <t>3.6724e-15</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H17" t="n">
-        <v>0.20379</v>
+        <v>0.19951</v>
       </c>
     </row>
     <row r="18">
@@ -1060,29 +1063,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.4607e-01</t>
+          <t>1.4703e-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.8065e-07</t>
+          <t>1.4311e-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.0907e-01</t>
+          <t>2.1137e-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5.8383e-14</t>
+          <t>2.7743e-14</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14607</v>
+        <v>0.14703</v>
       </c>
     </row>
     <row r="19">
@@ -1096,29 +1099,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4015e-01</t>
+          <t>1.4138e-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.6021e-07</t>
+          <t>4.2586e-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7521e-01</t>
+          <t>1.7769e-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.5139e-10</t>
+          <t>1.8384e-10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14015</v>
+        <v>0.14138</v>
       </c>
     </row>
     <row r="20">
@@ -1132,29 +1135,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.2574e-01</t>
+          <t>-1.2476e-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.2745e-06</t>
+          <t>8.3015e-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.3374e-01</t>
+          <t>-1.3119e-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.8099e-06</t>
+          <t>2.7426e-06</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12574</v>
+        <v>0.12476</v>
       </c>
     </row>
     <row r="21">
@@ -1168,29 +1171,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.2290e-01</t>
+          <t>-1.2317e-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.1673e-05</t>
+          <t>1.0813e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-1.8374e-01</t>
+          <t>-1.8283e-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.5564e-11</t>
+          <t>5.3119e-11</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1229</v>
+        <v>0.12317</v>
       </c>
     </row>
     <row r="22">
@@ -1199,34 +1202,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>p90_p10_ratio</t>
+          <t>wavelet_cD2_std</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.1847e-01</t>
+          <t>1.1766e-01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.3947e-05</t>
+          <t>2.6460e-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-1.2591e-01</t>
+          <t>1.7262e-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7.0652e-06</t>
+          <t>6.0286e-10</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.11847</v>
+        <v>0.11766</v>
       </c>
     </row>
     <row r="23">
@@ -1235,34 +1238,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wavelet_cD2_std</t>
+          <t>p90_p10_ratio</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.1641e-01</t>
+          <t>-1.1704e-01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.3221e-05</t>
+          <t>2.9192e-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7002e-01</t>
+          <t>-1.2179e-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.1624e-09</t>
+          <t>1.3580e-05</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H23" t="n">
-        <v>0.11641</v>
+        <v>0.11704</v>
       </c>
     </row>
     <row r="24">
@@ -1276,29 +1279,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1251e-01</t>
+          <t>1.1284e-01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.0603e-05</t>
+          <t>5.6120e-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.0403e-01</t>
+          <t>2.0398e-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.3587e-13</t>
+          <t>2.1941e-13</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H24" t="n">
-        <v>0.11251</v>
+        <v>0.11284</v>
       </c>
     </row>
     <row r="25">
@@ -1312,29 +1315,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.0665e-01</t>
+          <t>1.0493e-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.4459e-04</t>
+          <t>1.8075e-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.8321e-02</t>
+          <t>8.5310e-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.6647e-03</t>
+          <t>2.3536e-03</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H25" t="n">
-        <v>0.10665</v>
+        <v>0.10493</v>
       </c>
     </row>
     <row r="26">
@@ -1348,29 +1351,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.0129e-01</t>
+          <t>1.0204e-01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.0805e-04</t>
+          <t>2.7180e-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.9805e-01</t>
+          <t>2.0098e-01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.1807e-12</t>
+          <t>4.9628e-13</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H26" t="n">
-        <v>0.10129</v>
+        <v>0.10204</v>
       </c>
     </row>
     <row r="27">
@@ -1384,29 +1387,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9.8708e-02</t>
+          <t>9.9699e-02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.3836e-04</t>
+          <t>3.7518e-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.1474e-01</t>
+          <t>1.1484e-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4.3044e-05</t>
+          <t>4.1250e-05</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H27" t="n">
-        <v>0.098708</v>
+        <v>0.099699</v>
       </c>
     </row>
     <row r="28">
@@ -1420,29 +1423,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9.1249e-02</t>
+          <t>9.2198e-02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.1580e-03</t>
+          <t>1.0085e-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5812e-01</t>
+          <t>1.6327e-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1.5685e-08</t>
+          <t>4.9257e-09</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H28" t="n">
-        <v>0.091249</v>
+        <v>0.092198</v>
       </c>
     </row>
     <row r="29">
@@ -1451,34 +1454,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fft_mag_mean</t>
+          <t>wavelet_cD3_energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8.5660e-02</t>
+          <t>8.5577e-02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.2942e-03</t>
+          <t>2.2799e-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.5316e-02</t>
+          <t>1.3150e-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4.9186e-02</t>
+          <t>2.5971e-06</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H29" t="n">
-        <v>0.08566</v>
+        <v>0.085577</v>
       </c>
     </row>
     <row r="30">
@@ -1492,29 +1495,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8.4760e-02</t>
+          <t>8.3945e-02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.5520e-03</t>
+          <t>2.7652e-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.5455e-02</t>
+          <t>5.2441e-02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4.8619e-02</t>
+          <t>6.1825e-02</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08476</v>
+        <v>0.08394500000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1523,34 +1526,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wavelet_cD3_energy</t>
+          <t>fft_mag_mean</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8.4606e-02</t>
+          <t>8.3023e-02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.5988e-03</t>
+          <t>3.0792e-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3194e-01</t>
+          <t>5.1317e-02</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2.4917e-06</t>
+          <t>6.7630e-02</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H31" t="n">
-        <v>0.084606</v>
+        <v>0.083023</v>
       </c>
     </row>
     <row r="32">
@@ -1559,34 +1562,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>band1_energy</t>
+          <t>valley_count</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8.0972e-02</t>
+          <t>8.1186e-02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.9539e-03</t>
+          <t>3.8035e-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.5059e-02</t>
+          <t>1.0913e-01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5.0252e-02</t>
+          <t>9.8118e-05</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H32" t="n">
-        <v>0.080972</v>
+        <v>0.08118599999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1595,34 +1598,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>valley_count</t>
+          <t>band1_energy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7.9113e-02</t>
+          <t>8.0156e-02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.8712e-03</t>
+          <t>4.2744e-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.0346e-01</t>
+          <t>5.2075e-02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2.2792e-04</t>
+          <t>6.3667e-02</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H33" t="n">
-        <v>0.079113</v>
+        <v>0.08015600000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1631,34 +1634,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fft_mag_std</t>
+          <t>peak_count</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7.8868e-02</t>
+          <t>7.6868e-02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5.0055e-03</t>
+          <t>6.1512e-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4.3920e-02</t>
+          <t>8.9378e-02</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.1846e-01</t>
+          <t>1.4368e-03</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H34" t="n">
-        <v>0.07886799999999999</v>
+        <v>0.07686800000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1667,34 +1670,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>peak_count</t>
+          <t>fft_mag_std</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7.4581e-02</t>
+          <t>7.6685e-02</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7.9619e-03</t>
+          <t>6.2743e-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8.4104e-02</t>
+          <t>4.1567e-02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2.7566e-03</t>
+          <t>1.3890e-01</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H35" t="n">
-        <v>0.07458099999999999</v>
+        <v>0.076685</v>
       </c>
     </row>
     <row r="36">
@@ -1703,34 +1706,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kurtosis</t>
+          <t>band2_energy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.1051e-02</t>
+          <t>7.0303e-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.1480e-02</t>
+          <t>1.2244e-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8797e-01</t>
+          <t>3.8507e-02</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.5952e-11</t>
+          <t>1.7041e-01</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H36" t="n">
-        <v>0.071051</v>
+        <v>0.070303</v>
       </c>
     </row>
     <row r="37">
@@ -1739,34 +1742,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>band2_energy</t>
+          <t>kurtosis</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7.0927e-02</t>
+          <t>6.6054e-02</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.1625e-02</t>
+          <t>1.8608e-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4.3298e-02</t>
+          <t>1.8362e-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.2376e-01</t>
+          <t>4.3720e-11</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H37" t="n">
-        <v>0.070927</v>
+        <v>0.066054</v>
       </c>
     </row>
     <row r="38">
@@ -1780,29 +1783,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6.7671e-02</t>
+          <t>6.5714e-02</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.6075e-02</t>
+          <t>1.9225e-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.7192e-02</t>
+          <t>3.4743e-02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.8618e-01</t>
+          <t>2.1616e-01</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H38" t="n">
-        <v>0.067671</v>
+        <v>0.06571399999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1816,29 +1819,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6.7117e-02</t>
+          <t>6.4630e-02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.6964e-02</t>
+          <t>2.1309e-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>7.5958e-02</t>
+          <t>7.1935e-02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6.8753e-03</t>
+          <t>1.0367e-02</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H39" t="n">
-        <v>0.067117</v>
+        <v>0.06463000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1847,34 +1850,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>peak_max_width</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6.5346e-02</t>
+          <t>6.2232e-02</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.0107e-02</t>
+          <t>2.6632e-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.0568e-01</t>
+          <t>3.3160e-02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.6615e-04</t>
+          <t>2.3784e-01</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H40" t="n">
-        <v>0.065346</v>
+        <v>0.062232</v>
       </c>
     </row>
     <row r="41">
@@ -1883,34 +1886,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>std</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6.4257e-02</t>
+          <t>6.2145e-02</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.2283e-02</t>
+          <t>2.6846e-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.5192e-02</t>
+          <t>3.3147e-02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2.1100e-01</t>
+          <t>2.3802e-01</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06425699999999999</v>
+        <v>0.062145</v>
       </c>
     </row>
     <row r="42">
@@ -1919,34 +1922,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>std</t>
+          <t>peak_last_pos</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6.4166e-02</t>
+          <t>6.1620e-02</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.2473e-02</t>
+          <t>2.8162e-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.5177e-02</t>
+          <t>2.7695e-02</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2.1119e-01</t>
+          <t>3.2424e-01</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H42" t="n">
-        <v>0.064166</v>
+        <v>0.06162</v>
       </c>
     </row>
     <row r="43">
@@ -1955,34 +1958,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>peak_last_pos</t>
+          <t>peak_max_width</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5.9961e-02</t>
+          <t>6.1010e-02</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3.2971e-02</t>
+          <t>2.9763e-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2.4785e-02</t>
+          <t>9.9608e-02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3.7844e-01</t>
+          <t>3.7988e-04</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H43" t="n">
-        <v>0.059961</v>
+        <v>0.06101</v>
       </c>
     </row>
     <row r="44">
@@ -1996,29 +1999,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5.8675e-02</t>
+          <t>5.7737e-02</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.6924e-02</t>
+          <t>3.9737e-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.9434e-01</t>
+          <t>1.8779e-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3.1294e-12</t>
+          <t>1.5492e-11</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H44" t="n">
-        <v>0.058675</v>
+        <v>0.057737</v>
       </c>
     </row>
     <row r="45">
@@ -2032,29 +2035,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5.5413e-02</t>
+          <t>5.5155e-02</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.8789e-02</t>
+          <t>4.9489e-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.2181e-02</t>
+          <t>2.7637e-02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2.5273e-01</t>
+          <t>3.2524e-01</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H45" t="n">
-        <v>0.055413</v>
+        <v>0.055155</v>
       </c>
     </row>
     <row r="46">
@@ -2063,34 +2066,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>skewness</t>
+          <t>fft_mag_max</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-5.0928e-02</t>
+          <t>4.8447e-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7.0180e-02</t>
+          <t>8.4504e-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-6.5750e-02</t>
+          <t>1.4417e-02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.9349e-02</t>
+          <t>6.0788e-01</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H46" t="n">
-        <v>0.050928</v>
+        <v>0.048447</v>
       </c>
     </row>
     <row r="47">
@@ -2099,34 +2102,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fft_mag_max</t>
+          <t>first_high_pos</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5.0362e-02</t>
+          <t>4.8275e-02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7.3360e-02</t>
+          <t>8.5611e-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.6125e-02</t>
+          <t>2.5289e-02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5.6665e-01</t>
+          <t>3.6806e-01</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H47" t="n">
-        <v>0.050362</v>
+        <v>0.048275</v>
       </c>
     </row>
     <row r="48">
@@ -2140,29 +2143,29 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4.8007e-02</t>
+          <t>4.8186e-02</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.7865e-02</t>
+          <t>8.6193e-02</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.9256e-01</t>
+          <t>1.9442e-01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4.9583e-12</t>
+          <t>2.8312e-12</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H48" t="n">
-        <v>0.048007</v>
+        <v>0.048186</v>
       </c>
     </row>
     <row r="49">
@@ -2171,34 +2174,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>first_high_pos</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>4.6881e-02</t>
+          <t>-4.4707e-02</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.5578e-02</t>
+          <t>1.1142e-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2.3622e-02</t>
+          <t>-5.9902e-02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4.0122e-01</t>
+          <t>3.2867e-02</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H49" t="n">
-        <v>0.046881</v>
+        <v>0.044707</v>
       </c>
     </row>
     <row r="50">
@@ -2207,34 +2210,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>band4_energy</t>
+          <t>dominant_freq</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4.4523e-02</t>
+          <t>4.4654e-02</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.1348e-01</t>
+          <t>1.1185e-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.3737e-02</t>
+          <t>-5.9083e-02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3.9893e-01</t>
+          <t>3.5336e-02</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H50" t="n">
-        <v>0.044523</v>
+        <v>0.044654</v>
       </c>
     </row>
     <row r="51">
@@ -2243,34 +2246,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dominant_freq</t>
+          <t>band4_energy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4.4317e-02</t>
+          <t>4.4447e-02</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.1516e-01</t>
+          <t>1.1352e-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-6.2843e-02</t>
+          <t>1.9205e-02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2.5409e-02</t>
+          <t>4.9427e-01</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H51" t="n">
-        <v>0.044317</v>
+        <v>0.044447</v>
       </c>
     </row>
     <row r="52">
@@ -2279,34 +2282,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>peak_std_height</t>
+          <t>spectral_centroid</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4.2509e-02</t>
+          <t>4.1795e-02</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.3077e-01</t>
+          <t>1.3674e-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3452e-02</t>
+          <t>6.1304e-02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>6.3266e-01</t>
+          <t>2.8983e-02</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H52" t="n">
-        <v>0.042509</v>
+        <v>0.041795</v>
       </c>
     </row>
     <row r="53">
@@ -2315,34 +2318,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>spectral_centroid</t>
+          <t>peak_std_height</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4.2046e-02</t>
+          <t>4.1312e-02</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.3501e-01</t>
+          <t>1.4134e-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6.3285e-02</t>
+          <t>1.6559e-02</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2.4393e-02</t>
+          <t>5.5563e-01</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H53" t="n">
-        <v>0.042046</v>
+        <v>0.041312</v>
       </c>
     </row>
     <row r="54">
@@ -2351,34 +2354,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mean_abs_deviation</t>
+          <t>wavelet_cD1_energy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4.0496e-02</t>
+          <t>3.9589e-02</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.5002e-01</t>
+          <t>1.5871e-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.1382e-02</t>
+          <t>1.8697e-01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6.8589e-01</t>
+          <t>1.9022e-11</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.040496</v>
+        <v>0.039589</v>
       </c>
     </row>
     <row r="55">
@@ -2387,34 +2390,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>wavelet_cD1_energy</t>
+          <t>wavelet_energy_ratio_D1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.9561e-02</t>
+          <t>3.9187e-02</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.5966e-01</t>
+          <t>1.6298e-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.8230e-01</t>
+          <t>2.0808e-02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>6.4734e-11</t>
+          <t>4.5895e-01</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H55" t="n">
-        <v>0.039561</v>
+        <v>0.039187</v>
       </c>
     </row>
     <row r="56">
@@ -2423,34 +2426,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>wavelet_energy_ratio_D1</t>
+          <t>mean_abs_deviation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.9153e-02</t>
+          <t>3.8507e-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.6401e-01</t>
+          <t>1.7040e-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4208e-02</t>
+          <t>1.0225e-02</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>6.1366e-01</t>
+          <t>7.1593e-01</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H56" t="n">
-        <v>0.039153</v>
+        <v>0.038507</v>
       </c>
     </row>
     <row r="57">
@@ -2464,29 +2467,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.7599e-02</t>
+          <t>3.6788e-02</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.8141e-01</t>
+          <t>1.9032e-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.9002e-02</t>
+          <t>5.5615e-02</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>3.5882e-02</t>
+          <t>4.7618e-02</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H57" t="n">
-        <v>0.037599</v>
+        <v>0.036788</v>
       </c>
     </row>
     <row r="58">
@@ -2500,29 +2503,29 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.3539e-02</t>
+          <t>3.5225e-02</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.3325e-01</t>
+          <t>2.0986e-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6.5961e-02</t>
+          <t>6.9101e-02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.8962e-02</t>
+          <t>1.3813e-02</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H58" t="n">
-        <v>0.033539</v>
+        <v>0.035225</v>
       </c>
     </row>
     <row r="59">
@@ -2531,34 +2534,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>peak_first_pos</t>
+          <t>band4_energy_ratio</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2.4679e-02</t>
+          <t>2.2584e-02</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.8048e-01</t>
+          <t>4.2151e-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.7882e-03</t>
+          <t>-1.4593e-02</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>8.6490e-01</t>
+          <t>6.0352e-01</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H59" t="n">
-        <v>0.024679</v>
+        <v>0.022584</v>
       </c>
     </row>
     <row r="60">
@@ -2567,34 +2570,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>band4_energy_ratio</t>
+          <t>band2_energy_ratio</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2.2996e-02</t>
+          <t>-1.9762e-02</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4.1382e-01</t>
+          <t>4.8184e-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>-1.2172e-02</t>
+          <t>9.2189e-03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>6.6538e-01</t>
+          <t>7.4285e-01</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H60" t="n">
-        <v>0.022996</v>
+        <v>0.019762</v>
       </c>
     </row>
     <row r="61">
@@ -2603,34 +2606,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>band2_energy_ratio</t>
+          <t>peak_first_pos</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>-1.9266e-02</t>
+          <t>1.9658e-02</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.9358e-01</t>
+          <t>4.8415e-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.1576e-02</t>
+          <t>-1.0542e-03</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>6.8083e-01</t>
+          <t>9.7007e-01</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H61" t="n">
-        <v>0.019266</v>
+        <v>0.019658</v>
       </c>
     </row>
     <row r="62">
@@ -2644,29 +2647,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-1.8423e-02</t>
+          <t>-1.8106e-02</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5.1268e-01</t>
+          <t>5.1931e-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-7.2997e-03</t>
+          <t>-4.9947e-03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>7.9535e-01</t>
+          <t>8.5892e-01</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H62" t="n">
-        <v>0.018423</v>
+        <v>0.018106</v>
       </c>
     </row>
     <row r="63">
@@ -2675,34 +2678,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IQR</t>
+          <t>peak_mean_width</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1.2940e-02</t>
+          <t>-1.1944e-02</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6.4565e-01</t>
+          <t>6.7079e-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-2.2099e-02</t>
+          <t>1.1753e-02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>4.3226e-01</t>
+          <t>6.7574e-01</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01294</v>
+        <v>0.011944</v>
       </c>
     </row>
     <row r="64">
@@ -2711,34 +2714,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>band3_energy_ratio</t>
+          <t>IQR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.0505e-02</t>
+          <t>1.1327e-02</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7.0895e-01</t>
+          <t>6.8686e-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.2774e-03</t>
+          <t>-2.1894e-02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>9.6380e-01</t>
+          <t>4.3583e-01</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H64" t="n">
-        <v>0.010505</v>
+        <v>0.011327</v>
       </c>
     </row>
     <row r="65">
@@ -2747,34 +2750,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>spectral_spread</t>
+          <t>band3_energy_ratio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>7.8983e-03</t>
+          <t>1.0100e-02</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7.7898e-01</t>
+          <t>7.1926e-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2.4393e-03</t>
+          <t>-1.0866e-03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>9.3093e-01</t>
+          <t>9.6915e-01</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0078983</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="66">
@@ -2783,34 +2786,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>peak_mean_width</t>
+          <t>spectral_spread</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-5.6066e-03</t>
+          <t>6.6583e-03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.4210e-01</t>
+          <t>8.1269e-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.8433e-02</t>
+          <t>2.5534e-04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5.1247e-01</t>
+          <t>9.9275e-01</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0056066</v>
+        <v>0.0066583</v>
       </c>
     </row>
   </sheetData>
@@ -2880,29 +2883,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.4966e-01</t>
+          <t>2.4430e-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.9851e-19</t>
+          <t>1.0629e-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.5726e-01</t>
+          <t>2.5064e-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.4355e-20</t>
+          <t>1.2475e-19</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.24966</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="3">
@@ -2911,34 +2914,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>min</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.4813e-01</t>
+          <t>2.4273e-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.3413e-19</t>
+          <t>1.7907e-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.5108e-01</t>
+          <t>2.3123e-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.2225e-19</t>
+          <t>7.2834e-17</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24813</v>
+        <v>0.24273</v>
       </c>
     </row>
     <row r="4">
@@ -2947,34 +2950,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.4697e-01</t>
+          <t>2.4228e-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.9386e-19</t>
+          <t>2.0812e-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.3674e-01</t>
+          <t>2.4467e-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.4235e-17</t>
+          <t>9.3993e-19</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24697</v>
+        <v>0.24228</v>
       </c>
     </row>
     <row r="5">
@@ -2988,29 +2991,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.4139e-01</t>
+          <t>2.3686e-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.1449e-18</t>
+          <t>1.2178e-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.3510e-01</t>
+          <t>2.2931e-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.4050e-17</t>
+          <t>1.3272e-16</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.24139</v>
+        <v>0.23686</v>
       </c>
     </row>
     <row r="6">
@@ -3019,34 +3022,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>AUC_normalized</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.3935e-01</t>
+          <t>2.3408e-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.1197e-18</t>
+          <t>2.9653e-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.3958e-01</t>
+          <t>2.2396e-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5.6872e-18</t>
+          <t>6.8585e-16</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H6" t="n">
-        <v>0.23935</v>
+        <v>0.23408</v>
       </c>
     </row>
     <row r="7">
@@ -3055,34 +3058,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AUC_normalized</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.3926e-01</t>
+          <t>2.3393e-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.2968e-18</t>
+          <t>3.1054e-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.3085e-01</t>
+          <t>2.2384e-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.1731e-17</t>
+          <t>7.1052e-16</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H7" t="n">
-        <v>0.23926</v>
+        <v>0.23393</v>
       </c>
     </row>
     <row r="8">
@@ -3091,34 +3094,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>median</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.3910e-01</t>
+          <t>2.3343e-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.6482e-18</t>
+          <t>3.6385e-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.3072e-01</t>
+          <t>2.3202e-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.5549e-17</t>
+          <t>5.6859e-17</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2391</v>
+        <v>0.23343</v>
       </c>
     </row>
     <row r="9">
@@ -3132,29 +3135,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.3284e-01</t>
+          <t>2.2908e-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.9057e-17</t>
+          <t>1.4244e-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.1505e-01</t>
+          <t>2.0905e-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.0596e-14</t>
+          <t>5.3505e-14</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H9" t="n">
-        <v>0.23284</v>
+        <v>0.22908</v>
       </c>
     </row>
     <row r="10">
@@ -3168,29 +3171,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.2811e-01</t>
+          <t>2.2395e-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.1466e-16</t>
+          <t>6.8832e-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.1821e-01</t>
+          <t>2.1194e-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.2205e-15</t>
+          <t>2.3563e-14</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H10" t="n">
-        <v>0.22811</v>
+        <v>0.22395</v>
       </c>
     </row>
     <row r="11">
@@ -3204,29 +3207,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.2113e-01</t>
+          <t>2.1758e-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.7811e-15</t>
+          <t>4.6045e-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.0606e-01</t>
+          <t>2.0004e-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.3509e-13</t>
+          <t>6.3992e-13</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H11" t="n">
-        <v>0.22113</v>
+        <v>0.21758</v>
       </c>
     </row>
     <row r="12">
@@ -3235,34 +3238,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.1937e-01</t>
+          <t>2.1490e-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0002e-15</t>
+          <t>1.0063e-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.0271e-01</t>
+          <t>1.9810e-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3.3778e-13</t>
+          <t>1.0739e-12</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H12" t="n">
-        <v>0.21937</v>
+        <v>0.2149</v>
       </c>
     </row>
     <row r="13">
@@ -3271,34 +3274,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>p95</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.1868e-01</t>
+          <t>2.1435e-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.6821e-15</t>
+          <t>1.1788e-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.0424e-01</t>
+          <t>1.9569e-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.2287e-13</t>
+          <t>2.0305e-12</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H13" t="n">
-        <v>0.21868</v>
+        <v>0.21435</v>
       </c>
     </row>
     <row r="14">
@@ -3312,29 +3315,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.1696e-01</t>
+          <t>2.1285e-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.0931e-15</t>
+          <t>1.8171e-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.0137e-01</t>
+          <t>1.9507e-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.8537e-13</t>
+          <t>2.3932e-12</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H14" t="n">
-        <v>0.21696</v>
+        <v>0.21285</v>
       </c>
     </row>
     <row r="15">
@@ -3348,29 +3351,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.0892e-01</t>
+          <t>2.0406e-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6.0885e-14</t>
+          <t>2.1440e-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.2298e-01</t>
+          <t>2.1604e-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.0227e-15</t>
+          <t>7.2167e-15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H15" t="n">
-        <v>0.20892</v>
+        <v>0.20406</v>
       </c>
     </row>
     <row r="16">
@@ -3384,29 +3387,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.0849e-01</t>
+          <t>2.0380e-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.8648e-14</t>
+          <t>2.3007e-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.2891e-01</t>
+          <t>2.2181e-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.6781e-16</t>
+          <t>1.3105e-15</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.20849</v>
+        <v>0.2038</v>
       </c>
     </row>
     <row r="17">
@@ -3420,29 +3423,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.0379e-01</t>
+          <t>1.9951e-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.5190e-13</t>
+          <t>7.3758e-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.2539e-01</t>
+          <t>2.1835e-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4.9412e-16</t>
+          <t>3.6724e-15</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H17" t="n">
-        <v>0.20379</v>
+        <v>0.19951</v>
       </c>
     </row>
     <row r="18">
@@ -3456,29 +3459,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.4607e-01</t>
+          <t>1.4703e-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.8065e-07</t>
+          <t>1.4311e-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.0907e-01</t>
+          <t>2.1137e-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5.8383e-14</t>
+          <t>2.7743e-14</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14607</v>
+        <v>0.14703</v>
       </c>
     </row>
     <row r="19">
@@ -3492,29 +3495,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4015e-01</t>
+          <t>1.4138e-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.6021e-07</t>
+          <t>4.2586e-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7521e-01</t>
+          <t>1.7769e-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.5139e-10</t>
+          <t>1.8384e-10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14015</v>
+        <v>0.14138</v>
       </c>
     </row>
     <row r="20">
@@ -3528,29 +3531,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.2574e-01</t>
+          <t>-1.2476e-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.2745e-06</t>
+          <t>8.3015e-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.3374e-01</t>
+          <t>-1.3119e-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.8099e-06</t>
+          <t>2.7426e-06</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12574</v>
+        <v>0.12476</v>
       </c>
     </row>
     <row r="21">
@@ -3564,29 +3567,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.2290e-01</t>
+          <t>-1.2317e-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.1673e-05</t>
+          <t>1.0813e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-1.8374e-01</t>
+          <t>-1.8283e-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.5564e-11</t>
+          <t>5.3119e-11</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1229</v>
+        <v>0.12317</v>
       </c>
     </row>
   </sheetData>
@@ -3600,7 +3603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,6 +3617,11 @@
           <t>VIF</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3622,7 +3630,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.545</v>
+        <v>66.68000000000001</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3632,7 +3645,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.697</v>
+        <v>61.738</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3642,7 +3660,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.605</v>
+        <v>2.618</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3652,7 +3675,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.355</v>
+        <v>1.362</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3664,6 +3692,11 @@
       <c r="B6" t="n">
         <v>1.109</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3672,7 +3705,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.057</v>
+        <v>1.056</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3682,7 +3720,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.049</v>
+        <v>1.05</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3696,6 +3739,491 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>VIF</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>p25</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>61.738</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>slope_abs_mean</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PatientAge</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>p25</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>66.447</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean 제외, AUC_normalized 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AUC_normalized</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>61.532</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>mean 제외, AUC_normalized 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mean 제외, AUC_normalized 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mean 제외, AUC_normalized 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>slope_abs_mean</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mean 제외, AUC_normalized 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mean 제외, AUC_normalized 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PatientAge</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>mean 제외, AUC_normalized 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>p25</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>slope_abs_mean</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.056</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PatientAge</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AUC_normalized 제외, mean 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>51391.103</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AUC_normalized</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>51219.635</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>p25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>66.756</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>slope_abs_mean</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PatientAge</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mean + AUC_normalized 둘 다 포함</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3800,13 +4328,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C3" t="n">
-        <v>104.41</v>
+        <v>104.33</v>
       </c>
       <c r="D3" t="n">
-        <v>15.47</v>
+        <v>15.46</v>
       </c>
       <c r="E3" t="n">
         <v>29</v>
@@ -3815,7 +4343,7 @@
         <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="H3" t="n">
         <v>114</v>
@@ -3828,6 +4356,732 @@
       </c>
       <c r="K3" t="n">
         <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>iCT 256</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>278</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition Flash</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>271</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition AS+</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>202</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SOMATOM Force</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>177</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Revolution EVO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sensation 64</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LightSpeed VCT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>48</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Discovery CT750 HD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Revolution CT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brilliance 64</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aquilion ONE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aquilion</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SOMATOM Perspective</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ingenuity Core 128</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aquilion PRIME</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Optima CT660</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ingenuity CT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sensation Open</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition Edge</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ingenuity Core</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ingenuity CT Elite</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SOMATOM Scope</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition AS</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aquilion/LB</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Alexion</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brivo CT385 Series</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spirit</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Activion16</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Supria</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brilliance 40</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Aquilion Lightning</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Revolution HD</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sensation 16</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SOMATOM Emotion 16</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ECLOS</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GMS Revolution FT</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Emotion 16</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>iCT SP</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SOMATOM go.Top</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Definition Edge</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MX 16</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Emotion 16 (2007)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SOMATOM Drive</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Revolution Frontier</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kVp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>956</v>
+      </c>
+      <c r="C4" t="n">
+        <v>75.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120</v>
+      </c>
+      <c r="B6" t="n">
+        <v>250</v>
+      </c>
+      <c r="C6" t="n">
+        <v>19.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130</v>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/aec/results/신촌/feature_selection_report.xlsx
+++ b/연구코드/aec/results/신촌/feature_selection_report.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상관계수_Top20" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIF_선택feature" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIF_부분제거_비교" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAMA_분포_성별" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CT_스캐너_분포" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kVp_분포" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correlation_Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAMA_분포_성별" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CT_스캐너_분포" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kVp_분포" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,12 +488,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.4430e-01</t>
+          <t>2.4419e-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0629e-18</t>
+          <t>1.1046e-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -502,14 +503,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.2475e-19</t>
+          <t>1.2473e-19</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2443</v>
+        <v>0.24419</v>
       </c>
     </row>
     <row r="3">
@@ -523,12 +524,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.4273e-01</t>
+          <t>2.4271e-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.7907e-18</t>
+          <t>1.8024e-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -538,14 +539,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7.2834e-17</t>
+          <t>7.2833e-17</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24273</v>
+        <v>0.24271</v>
       </c>
     </row>
     <row r="4">
@@ -559,12 +560,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.4228e-01</t>
+          <t>2.4219e-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0812e-18</t>
+          <t>2.1441e-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -574,14 +575,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.3993e-19</t>
+          <t>9.3979e-19</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24228</v>
+        <v>0.24219</v>
       </c>
     </row>
     <row r="5">
@@ -595,12 +596,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.3686e-01</t>
+          <t>2.3680e-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.2178e-17</t>
+          <t>1.2407e-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -610,14 +611,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.3272e-16</t>
+          <t>1.3270e-16</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.23686</v>
+        <v>0.2368</v>
       </c>
     </row>
     <row r="6">
@@ -631,12 +632,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.3408e-01</t>
+          <t>2.3381e-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.9653e-17</t>
+          <t>3.2278e-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,14 +647,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6.8585e-16</t>
+          <t>6.8599e-16</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1269</v>
       </c>
       <c r="H6" t="n">
-        <v>0.23408</v>
+        <v>0.23381</v>
       </c>
     </row>
     <row r="7">
@@ -667,12 +668,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.3393e-01</t>
+          <t>2.3366e-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.1054e-17</t>
+          <t>3.3843e-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -682,14 +683,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7.1052e-16</t>
+          <t>7.1069e-16</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1269</v>
       </c>
       <c r="H7" t="n">
-        <v>0.23393</v>
+        <v>0.23366</v>
       </c>
     </row>
     <row r="8">
@@ -703,12 +704,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.3343e-01</t>
+          <t>2.3320e-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.6385e-17</t>
+          <t>3.9182e-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -718,14 +719,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5.6859e-17</t>
+          <t>5.6870e-17</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1269</v>
       </c>
       <c r="H8" t="n">
-        <v>0.23343</v>
+        <v>0.2332</v>
       </c>
     </row>
     <row r="9">
@@ -739,12 +740,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.2908e-01</t>
+          <t>2.2876e-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.4244e-16</t>
+          <t>1.5748e-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -754,14 +755,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5.3505e-14</t>
+          <t>5.3532e-14</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1269</v>
       </c>
       <c r="H9" t="n">
-        <v>0.22908</v>
+        <v>0.22876</v>
       </c>
     </row>
     <row r="10">
@@ -775,12 +776,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.2395e-01</t>
+          <t>2.2364e-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.8832e-16</t>
+          <t>7.5648e-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -790,14 +791,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.3563e-14</t>
+          <t>2.3577e-14</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1269</v>
       </c>
       <c r="H10" t="n">
-        <v>0.22395</v>
+        <v>0.22364</v>
       </c>
     </row>
     <row r="11">
@@ -811,29 +812,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.1758e-01</t>
+          <t>2.1718e-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.6045e-15</t>
+          <t>5.1697e-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.0004e-01</t>
+          <t>2.0003e-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.3992e-13</t>
+          <t>6.4021e-13</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1269</v>
       </c>
       <c r="H11" t="n">
-        <v>0.21758</v>
+        <v>0.21718</v>
       </c>
     </row>
     <row r="12">
@@ -847,12 +848,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.1490e-01</t>
+          <t>2.1453e-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0063e-14</t>
+          <t>1.1194e-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -862,14 +863,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.0739e-12</t>
+          <t>1.0743e-12</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1269</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2149</v>
+        <v>0.21453</v>
       </c>
     </row>
     <row r="13">
@@ -883,12 +884,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.1435e-01</t>
+          <t>2.1395e-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.1788e-14</t>
+          <t>1.3245e-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -898,14 +899,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.0305e-12</t>
+          <t>2.0313e-12</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1269</v>
       </c>
       <c r="H13" t="n">
-        <v>0.21435</v>
+        <v>0.21395</v>
       </c>
     </row>
     <row r="14">
@@ -919,29 +920,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.1285e-01</t>
+          <t>2.1249e-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.8171e-14</t>
+          <t>2.0147e-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.9507e-01</t>
+          <t>1.9506e-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.3932e-12</t>
+          <t>2.3940e-12</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1269</v>
       </c>
       <c r="H14" t="n">
-        <v>0.21285</v>
+        <v>0.21249</v>
       </c>
     </row>
     <row r="15">
@@ -955,29 +956,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.0406e-01</t>
+          <t>2.0419e-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.1440e-13</t>
+          <t>2.0704e-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.1604e-01</t>
+          <t>2.1605e-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.2167e-15</t>
+          <t>7.2079e-15</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1269</v>
       </c>
       <c r="H15" t="n">
-        <v>0.20406</v>
+        <v>0.20419</v>
       </c>
     </row>
     <row r="16">
@@ -991,12 +992,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.0380e-01</t>
+          <t>2.0382e-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.3007e-13</t>
+          <t>2.2887e-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1006,14 +1007,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.3105e-15</t>
+          <t>1.3099e-15</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2038</v>
+        <v>0.20382</v>
       </c>
     </row>
     <row r="17">
@@ -1027,12 +1028,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.9951e-01</t>
+          <t>1.9947e-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.3758e-13</t>
+          <t>7.4535e-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1042,14 +1043,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3.6724e-15</t>
+          <t>3.6718e-15</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1269</v>
       </c>
       <c r="H17" t="n">
-        <v>0.19951</v>
+        <v>0.19947</v>
       </c>
     </row>
     <row r="18">
@@ -1063,12 +1064,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.4703e-01</t>
+          <t>1.4697e-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.4311e-07</t>
+          <t>1.4491e-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1078,14 +1079,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.7743e-14</t>
+          <t>2.7762e-14</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1269</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14703</v>
+        <v>0.14697</v>
       </c>
     </row>
     <row r="19">
@@ -1099,12 +1100,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4138e-01</t>
+          <t>1.4192e-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.2586e-07</t>
+          <t>3.8490e-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1114,14 +1115,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.8384e-10</t>
+          <t>1.8362e-10</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1269</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14138</v>
+        <v>0.14192</v>
       </c>
     </row>
     <row r="20">
@@ -1135,29 +1136,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.2476e-01</t>
+          <t>-1.2574e-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3015e-06</t>
+          <t>7.0319e-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.3119e-01</t>
+          <t>-1.3120e-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.7426e-06</t>
+          <t>2.7417e-06</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12476</v>
+        <v>0.12574</v>
       </c>
     </row>
     <row r="21">
@@ -1171,12 +1172,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.2317e-01</t>
+          <t>-1.2273e-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.0813e-05</t>
+          <t>1.1632e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1186,14 +1187,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5.3119e-11</t>
+          <t>5.3182e-11</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1269</v>
       </c>
       <c r="H21" t="n">
-        <v>0.12317</v>
+        <v>0.12273</v>
       </c>
     </row>
     <row r="22">
@@ -1202,34 +1203,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wavelet_cD2_std</t>
+          <t>p90_p10_ratio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.1766e-01</t>
+          <t>-1.1789e-01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.6460e-05</t>
+          <t>2.5513e-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7262e-01</t>
+          <t>-1.2179e-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6.0286e-10</t>
+          <t>1.3580e-05</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.11766</v>
+        <v>0.11789</v>
       </c>
     </row>
     <row r="23">
@@ -1238,34 +1239,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>p90_p10_ratio</t>
+          <t>wavelet_cD2_std</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.1704e-01</t>
+          <t>1.1709e-01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.9192e-05</t>
+          <t>2.8960e-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-1.2179e-01</t>
+          <t>1.7261e-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.3580e-05</t>
+          <t>6.0388e-10</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1269</v>
       </c>
       <c r="H23" t="n">
-        <v>0.11704</v>
+        <v>0.11709</v>
       </c>
     </row>
     <row r="24">
@@ -1279,29 +1280,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.1284e-01</t>
+          <t>1.1273e-01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5.6120e-05</t>
+          <t>5.7080e-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.0398e-01</t>
+          <t>2.0397e-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.1941e-13</t>
+          <t>2.1971e-13</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1269</v>
       </c>
       <c r="H24" t="n">
-        <v>0.11284</v>
+        <v>0.11273</v>
       </c>
     </row>
     <row r="25">
@@ -1315,29 +1316,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.0493e-01</t>
+          <t>1.0433e-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.8075e-04</t>
+          <t>1.9683e-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.5310e-02</t>
+          <t>8.5307e-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2.3536e-03</t>
+          <t>2.3544e-03</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1269</v>
       </c>
       <c r="H25" t="n">
-        <v>0.10493</v>
+        <v>0.10433</v>
       </c>
     </row>
     <row r="26">
@@ -1351,29 +1352,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.0204e-01</t>
+          <t>1.0196e-01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.7180e-04</t>
+          <t>2.7475e-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.0098e-01</t>
+          <t>2.0097e-01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.9628e-13</t>
+          <t>4.9700e-13</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1269</v>
       </c>
       <c r="H26" t="n">
-        <v>0.10204</v>
+        <v>0.10196</v>
       </c>
     </row>
     <row r="27">
@@ -1387,29 +1388,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9.9699e-02</t>
+          <t>9.8951e-02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.7518e-04</t>
+          <t>4.1538e-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.1484e-01</t>
+          <t>1.1483e-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4.1250e-05</t>
+          <t>4.1311e-05</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1269</v>
       </c>
       <c r="H27" t="n">
-        <v>0.099699</v>
+        <v>0.098951</v>
       </c>
     </row>
     <row r="28">
@@ -1423,12 +1424,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9.2198e-02</t>
+          <t>9.2201e-02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.0085e-03</t>
+          <t>1.0081e-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1438,14 +1439,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4.9257e-09</t>
+          <t>4.9258e-09</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>1269</v>
       </c>
       <c r="H28" t="n">
-        <v>0.092198</v>
+        <v>0.09220100000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1459,29 +1460,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>8.5577e-02</t>
+          <t>8.5253e-02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.2799e-03</t>
+          <t>2.3696e-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3150e-01</t>
+          <t>1.3149e-01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.5971e-06</t>
+          <t>2.6012e-06</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1269</v>
       </c>
       <c r="H29" t="n">
-        <v>0.085577</v>
+        <v>0.085253</v>
       </c>
     </row>
     <row r="30">
@@ -1495,29 +1496,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8.3945e-02</t>
+          <t>8.3919e-02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.7652e-03</t>
+          <t>2.7734e-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>5.2441e-02</t>
+          <t>5.2442e-02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.1825e-02</t>
+          <t>6.1822e-02</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1269</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08394500000000001</v>
+        <v>0.08391899999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1531,29 +1532,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8.3023e-02</t>
+          <t>8.2214e-02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.0792e-03</t>
+          <t>3.3809e-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5.1317e-02</t>
+          <t>5.1311e-02</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6.7630e-02</t>
+          <t>6.7660e-02</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1269</v>
       </c>
       <c r="H31" t="n">
-        <v>0.083023</v>
+        <v>0.082214</v>
       </c>
     </row>
     <row r="32">
@@ -1567,29 +1568,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8.1186e-02</t>
+          <t>8.0767e-02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.8035e-03</t>
+          <t>3.9890e-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0913e-01</t>
+          <t>1.0912e-01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>9.8118e-05</t>
+          <t>9.8260e-05</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>1269</v>
       </c>
       <c r="H32" t="n">
-        <v>0.08118599999999999</v>
+        <v>0.08076700000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1603,29 +1604,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8.0156e-02</t>
+          <t>8.0117e-02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.2744e-03</t>
+          <t>4.2929e-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5.2075e-02</t>
+          <t>5.2076e-02</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6.3667e-02</t>
+          <t>6.3663e-02</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>1269</v>
       </c>
       <c r="H33" t="n">
-        <v>0.08015600000000001</v>
+        <v>0.08011699999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1639,29 +1640,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7.6868e-02</t>
+          <t>7.6434e-02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6.1512e-03</t>
+          <t>6.4473e-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8.9378e-02</t>
+          <t>8.9370e-02</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.4368e-03</t>
+          <t>1.4381e-03</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1269</v>
       </c>
       <c r="H34" t="n">
-        <v>0.07686800000000001</v>
+        <v>0.076434</v>
       </c>
     </row>
     <row r="35">
@@ -1675,17 +1676,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7.6685e-02</t>
+          <t>7.6236e-02</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6.2743e-03</t>
+          <t>6.5872e-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.1567e-02</t>
+          <t>4.1566e-02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1697,7 +1698,7 @@
         <v>1269</v>
       </c>
       <c r="H35" t="n">
-        <v>0.076685</v>
+        <v>0.076236</v>
       </c>
     </row>
     <row r="36">
@@ -1711,29 +1712,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7.0303e-02</t>
+          <t>7.0325e-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.2244e-02</t>
+          <t>1.2217e-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.8507e-02</t>
+          <t>3.8500e-02</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.7041e-01</t>
+          <t>1.7049e-01</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>1269</v>
       </c>
       <c r="H36" t="n">
-        <v>0.070303</v>
+        <v>0.070325</v>
       </c>
     </row>
     <row r="37">
@@ -1747,29 +1748,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.6054e-02</t>
+          <t>6.5966e-02</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.8608e-02</t>
+          <t>1.8765e-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.8362e-01</t>
+          <t>1.8363e-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.3720e-11</t>
+          <t>4.3680e-11</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>1269</v>
       </c>
       <c r="H37" t="n">
-        <v>0.066054</v>
+        <v>0.065966</v>
       </c>
     </row>
     <row r="38">
@@ -1783,29 +1784,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6.5714e-02</t>
+          <t>6.5045e-02</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1.9225e-02</t>
+          <t>2.0490e-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.4743e-02</t>
+          <t>3.4740e-02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.1616e-01</t>
+          <t>2.1620e-01</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1269</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06571399999999999</v>
+        <v>0.06504500000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1819,29 +1820,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6.4630e-02</t>
+          <t>6.4425e-02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.1309e-02</t>
+          <t>2.1726e-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>7.1935e-02</t>
+          <t>7.1936e-02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.0367e-02</t>
+          <t>1.0366e-02</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>1269</v>
       </c>
       <c r="H39" t="n">
-        <v>0.06463000000000001</v>
+        <v>0.064425</v>
       </c>
     </row>
     <row r="40">
@@ -1850,34 +1851,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>peak_max_width</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>6.2232e-02</t>
+          <t>6.2173e-02</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.6632e-02</t>
+          <t>2.6777e-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.3160e-02</t>
+          <t>9.9624e-02</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2.3784e-01</t>
+          <t>3.7905e-04</t>
         </is>
       </c>
       <c r="G40" t="n">
         <v>1269</v>
       </c>
       <c r="H40" t="n">
-        <v>0.062232</v>
+        <v>0.062173</v>
       </c>
     </row>
     <row r="41">
@@ -1886,34 +1887,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>std</t>
+          <t>peak_last_pos</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6.2145e-02</t>
+          <t>6.1743e-02</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2.6846e-02</t>
+          <t>2.7849e-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3.3147e-02</t>
+          <t>2.7697e-02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2.3802e-01</t>
+          <t>3.2420e-01</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>1269</v>
       </c>
       <c r="H41" t="n">
-        <v>0.062145</v>
+        <v>0.061743</v>
       </c>
     </row>
     <row r="42">
@@ -1922,34 +1923,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>peak_last_pos</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>6.1620e-02</t>
+          <t>6.1535e-02</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2.8162e-02</t>
+          <t>2.8381e-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2.7695e-02</t>
+          <t>3.3156e-02</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3.2424e-01</t>
+          <t>2.3789e-01</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>1269</v>
       </c>
       <c r="H42" t="n">
-        <v>0.06162</v>
+        <v>0.061535</v>
       </c>
     </row>
     <row r="43">
@@ -1958,34 +1959,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>peak_max_width</t>
+          <t>std</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>6.1010e-02</t>
+          <t>6.1447e-02</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.9763e-02</t>
+          <t>2.8609e-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.9608e-02</t>
+          <t>3.3143e-02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3.7988e-04</t>
+          <t>2.3807e-01</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>1269</v>
       </c>
       <c r="H43" t="n">
-        <v>0.06101</v>
+        <v>0.061447</v>
       </c>
     </row>
     <row r="44">
@@ -1999,29 +2000,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5.7737e-02</t>
+          <t>5.8377e-02</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.9737e-02</t>
+          <t>3.7589e-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8779e-01</t>
+          <t>1.8781e-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1.5492e-11</t>
+          <t>1.5423e-11</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>1269</v>
       </c>
       <c r="H44" t="n">
-        <v>0.057737</v>
+        <v>0.058377</v>
       </c>
     </row>
     <row r="45">
@@ -2035,29 +2036,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5.5155e-02</t>
+          <t>5.5248e-02</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.9489e-02</t>
+          <t>4.9105e-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.7637e-02</t>
+          <t>2.7630e-02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3.2524e-01</t>
+          <t>3.2537e-01</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>1269</v>
       </c>
       <c r="H45" t="n">
-        <v>0.055155</v>
+        <v>0.055248</v>
       </c>
     </row>
     <row r="46">
@@ -2066,34 +2067,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fft_mag_max</t>
+          <t>first_high_pos</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4.8447e-02</t>
+          <t>4.8653e-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.4504e-02</t>
+          <t>8.3184e-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4417e-02</t>
+          <t>2.5297e-02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6.0788e-01</t>
+          <t>3.6790e-01</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>1269</v>
       </c>
       <c r="H46" t="n">
-        <v>0.048447</v>
+        <v>0.048653</v>
       </c>
     </row>
     <row r="47">
@@ -2102,34 +2103,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>first_high_pos</t>
+          <t>wavelet_cD2_energy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4.8275e-02</t>
+          <t>4.8260e-02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.5611e-02</t>
+          <t>8.5711e-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2.5289e-02</t>
+          <t>1.9442e-01</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>3.6806e-01</t>
+          <t>2.8359e-12</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1269</v>
       </c>
       <c r="H47" t="n">
-        <v>0.048275</v>
+        <v>0.04826</v>
       </c>
     </row>
     <row r="48">
@@ -2138,34 +2139,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wavelet_cD2_energy</t>
+          <t>fft_mag_max</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4.8186e-02</t>
+          <t>4.7897e-02</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.6193e-02</t>
+          <t>8.8098e-02</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.9442e-01</t>
+          <t>1.4416e-02</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2.8312e-12</t>
+          <t>6.0791e-01</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>1269</v>
       </c>
       <c r="H48" t="n">
-        <v>0.048186</v>
+        <v>0.047897</v>
       </c>
     </row>
     <row r="49">
@@ -2174,34 +2175,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>skewness</t>
+          <t>dominant_freq</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>-4.4707e-02</t>
+          <t>4.5002e-02</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.1142e-01</t>
+          <t>1.0908e-01</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-5.9902e-02</t>
+          <t>-5.9084e-02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>3.2867e-02</t>
+          <t>3.5335e-02</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>1269</v>
       </c>
       <c r="H49" t="n">
-        <v>0.044707</v>
+        <v>0.045002</v>
       </c>
     </row>
     <row r="50">
@@ -2210,34 +2211,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dominant_freq</t>
+          <t>band4_energy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4.4654e-02</t>
+          <t>4.4561e-02</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.1185e-01</t>
+          <t>1.1260e-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-5.9083e-02</t>
+          <t>1.9198e-02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3.5336e-02</t>
+          <t>4.9442e-01</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1269</v>
       </c>
       <c r="H50" t="n">
-        <v>0.044654</v>
+        <v>0.044561</v>
       </c>
     </row>
     <row r="51">
@@ -2246,34 +2247,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>band4_energy</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4.4447e-02</t>
+          <t>-4.4044e-02</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.1352e-01</t>
+          <t>1.1684e-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.9205e-02</t>
+          <t>-5.9894e-02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4.9427e-01</t>
+          <t>3.2892e-02</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>1269</v>
       </c>
       <c r="H51" t="n">
-        <v>0.044447</v>
+        <v>0.044044</v>
       </c>
     </row>
     <row r="52">
@@ -2287,29 +2288,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4.1795e-02</t>
+          <t>4.1118e-02</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.3674e-01</t>
+          <t>1.4321e-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.1304e-02</t>
+          <t>6.1290e-02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2.8983e-02</t>
+          <t>2.9018e-02</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>1269</v>
       </c>
       <c r="H52" t="n">
-        <v>0.041795</v>
+        <v>0.041118</v>
       </c>
     </row>
     <row r="53">
@@ -2323,29 +2324,29 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4.1312e-02</t>
+          <t>4.1117e-02</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.4134e-01</t>
+          <t>1.4323e-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.6559e-02</t>
+          <t>1.6564e-02</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5.5563e-01</t>
+          <t>5.5552e-01</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>1269</v>
       </c>
       <c r="H53" t="n">
-        <v>0.041312</v>
+        <v>0.041117</v>
       </c>
     </row>
     <row r="54">
@@ -2359,29 +2360,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.9589e-02</t>
+          <t>3.9714e-02</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.5871e-01</t>
+          <t>1.5739e-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.8697e-01</t>
+          <t>1.8698e-01</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.9022e-11</t>
+          <t>1.9009e-11</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>1269</v>
       </c>
       <c r="H54" t="n">
-        <v>0.039589</v>
+        <v>0.039714</v>
       </c>
     </row>
     <row r="55">
@@ -2395,29 +2396,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.9187e-02</t>
+          <t>3.9310e-02</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.6298e-01</t>
+          <t>1.6166e-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2.0808e-02</t>
+          <t>2.0807e-02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>4.5895e-01</t>
+          <t>4.5897e-01</t>
         </is>
       </c>
       <c r="G55" t="n">
         <v>1269</v>
       </c>
       <c r="H55" t="n">
-        <v>0.039187</v>
+        <v>0.03931</v>
       </c>
     </row>
     <row r="56">
@@ -2431,29 +2432,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.8507e-02</t>
+          <t>3.7692e-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1.7040e-01</t>
+          <t>1.7964e-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.0225e-02</t>
+          <t>1.0221e-02</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.1593e-01</t>
+          <t>7.1605e-01</t>
         </is>
       </c>
       <c r="G56" t="n">
         <v>1269</v>
       </c>
       <c r="H56" t="n">
-        <v>0.038507</v>
+        <v>0.037692</v>
       </c>
     </row>
     <row r="57">
@@ -2462,34 +2463,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>spectral_rolloff</t>
+          <t>slope_mean</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.6788e-02</t>
+          <t>3.6297e-02</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.9032e-01</t>
+          <t>1.9630e-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.5615e-02</t>
+          <t>6.9110e-02</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4.7618e-02</t>
+          <t>1.3801e-02</t>
         </is>
       </c>
       <c r="G57" t="n">
         <v>1269</v>
       </c>
       <c r="H57" t="n">
-        <v>0.036788</v>
+        <v>0.036297</v>
       </c>
     </row>
     <row r="58">
@@ -2498,34 +2499,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>slope_mean</t>
+          <t>spectral_rolloff</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.5225e-02</t>
+          <t>3.6219e-02</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.0986e-01</t>
+          <t>1.9727e-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6.9101e-02</t>
+          <t>5.5607e-02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1.3813e-02</t>
+          <t>4.7650e-02</t>
         </is>
       </c>
       <c r="G58" t="n">
         <v>1269</v>
       </c>
       <c r="H58" t="n">
-        <v>0.035225</v>
+        <v>0.036219</v>
       </c>
     </row>
     <row r="59">
@@ -2539,29 +2540,29 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2.2584e-02</t>
+          <t>2.2051e-02</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4.2151e-01</t>
+          <t>4.3254e-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-1.4593e-02</t>
+          <t>-1.4607e-02</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>6.0352e-01</t>
+          <t>6.0315e-01</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>1269</v>
       </c>
       <c r="H59" t="n">
-        <v>0.022584</v>
+        <v>0.022051</v>
       </c>
     </row>
     <row r="60">
@@ -2575,29 +2576,29 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>-1.9762e-02</t>
+          <t>-2.0947e-02</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4.8184e-01</t>
+          <t>4.5595e-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>9.2189e-03</t>
+          <t>9.2041e-03</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>7.4285e-01</t>
+          <t>7.4324e-01</t>
         </is>
       </c>
       <c r="G60" t="n">
         <v>1269</v>
       </c>
       <c r="H60" t="n">
-        <v>0.019762</v>
+        <v>0.020947</v>
       </c>
     </row>
     <row r="61">
@@ -2611,29 +2612,29 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.9658e-02</t>
+          <t>1.9867e-02</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.8415e-01</t>
+          <t>4.7950e-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-1.0542e-03</t>
+          <t>-1.0468e-03</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>9.7007e-01</t>
+          <t>9.7028e-01</t>
         </is>
       </c>
       <c r="G61" t="n">
         <v>1269</v>
       </c>
       <c r="H61" t="n">
-        <v>0.019658</v>
+        <v>0.019867</v>
       </c>
     </row>
     <row r="62">
@@ -2647,29 +2648,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-1.8106e-02</t>
+          <t>-1.7470e-02</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5.1931e-01</t>
+          <t>5.3410e-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>-4.9947e-03</t>
+          <t>-4.9797e-03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>8.5892e-01</t>
+          <t>8.5934e-01</t>
         </is>
       </c>
       <c r="G62" t="n">
         <v>1269</v>
       </c>
       <c r="H62" t="n">
-        <v>0.018106</v>
+        <v>0.01747</v>
       </c>
     </row>
     <row r="63">
@@ -2678,34 +2679,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>peak_mean_width</t>
+          <t>IQR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-1.1944e-02</t>
+          <t>1.0525e-02</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6.7079e-01</t>
+          <t>7.0798e-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.1753e-02</t>
+          <t>-2.1898e-02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>6.7574e-01</t>
+          <t>4.3574e-01</t>
         </is>
       </c>
       <c r="G63" t="n">
         <v>1269</v>
       </c>
       <c r="H63" t="n">
-        <v>0.011944</v>
+        <v>0.010525</v>
       </c>
     </row>
     <row r="64">
@@ -2714,34 +2715,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IQR</t>
+          <t>peak_mean_width</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1.1327e-02</t>
+          <t>-1.0050e-02</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6.8686e-01</t>
+          <t>7.2059e-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>-2.1894e-02</t>
+          <t>1.1771e-02</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>4.3583e-01</t>
+          <t>6.7527e-01</t>
         </is>
       </c>
       <c r="G64" t="n">
         <v>1269</v>
       </c>
       <c r="H64" t="n">
-        <v>0.011327</v>
+        <v>0.01005</v>
       </c>
     </row>
     <row r="65">
@@ -2755,29 +2756,29 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.0100e-02</t>
+          <t>9.2018e-03</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>7.1926e-01</t>
+          <t>7.4330e-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-1.0866e-03</t>
+          <t>-1.1020e-03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>9.6915e-01</t>
+          <t>9.6872e-01</t>
         </is>
       </c>
       <c r="G65" t="n">
         <v>1269</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0101</v>
+        <v>0.0092018</v>
       </c>
     </row>
     <row r="66">
@@ -2791,29 +2792,29 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6.6583e-03</t>
+          <t>4.6526e-03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.1269e-01</t>
+          <t>8.6849e-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2.5534e-04</t>
+          <t>2.3975e-04</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>9.9275e-01</t>
+          <t>9.9319e-01</t>
         </is>
       </c>
       <c r="G66" t="n">
         <v>1269</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0066583</v>
+        <v>0.0046526</v>
       </c>
     </row>
   </sheetData>
@@ -2883,12 +2884,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.4430e-01</t>
+          <t>2.4419e-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.0629e-18</t>
+          <t>1.1046e-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2898,14 +2899,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.2475e-19</t>
+          <t>1.2473e-19</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>1269</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2443</v>
+        <v>0.24419</v>
       </c>
     </row>
     <row r="3">
@@ -2919,12 +2920,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.4273e-01</t>
+          <t>2.4271e-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.7907e-18</t>
+          <t>1.8024e-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2934,14 +2935,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7.2834e-17</t>
+          <t>7.2833e-17</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.24273</v>
+        <v>0.24271</v>
       </c>
     </row>
     <row r="4">
@@ -2955,12 +2956,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.4228e-01</t>
+          <t>2.4219e-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.0812e-18</t>
+          <t>2.1441e-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2970,14 +2971,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.3993e-19</t>
+          <t>9.3979e-19</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.24228</v>
+        <v>0.24219</v>
       </c>
     </row>
     <row r="5">
@@ -2991,12 +2992,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.3686e-01</t>
+          <t>2.3680e-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.2178e-17</t>
+          <t>1.2407e-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3006,14 +3007,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.3272e-16</t>
+          <t>1.3270e-16</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.23686</v>
+        <v>0.2368</v>
       </c>
     </row>
     <row r="6">
@@ -3027,12 +3028,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.3408e-01</t>
+          <t>2.3381e-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.9653e-17</t>
+          <t>3.2278e-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3042,14 +3043,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6.8585e-16</t>
+          <t>6.8599e-16</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1269</v>
       </c>
       <c r="H6" t="n">
-        <v>0.23408</v>
+        <v>0.23381</v>
       </c>
     </row>
     <row r="7">
@@ -3063,12 +3064,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.3393e-01</t>
+          <t>2.3366e-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.1054e-17</t>
+          <t>3.3843e-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,14 +3079,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7.1052e-16</t>
+          <t>7.1069e-16</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1269</v>
       </c>
       <c r="H7" t="n">
-        <v>0.23393</v>
+        <v>0.23366</v>
       </c>
     </row>
     <row r="8">
@@ -3099,12 +3100,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.3343e-01</t>
+          <t>2.3320e-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.6385e-17</t>
+          <t>3.9182e-17</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3114,14 +3115,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5.6859e-17</t>
+          <t>5.6870e-17</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1269</v>
       </c>
       <c r="H8" t="n">
-        <v>0.23343</v>
+        <v>0.2332</v>
       </c>
     </row>
     <row r="9">
@@ -3135,12 +3136,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.2908e-01</t>
+          <t>2.2876e-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.4244e-16</t>
+          <t>1.5748e-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3150,14 +3151,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5.3505e-14</t>
+          <t>5.3532e-14</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1269</v>
       </c>
       <c r="H9" t="n">
-        <v>0.22908</v>
+        <v>0.22876</v>
       </c>
     </row>
     <row r="10">
@@ -3171,12 +3172,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.2395e-01</t>
+          <t>2.2364e-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6.8832e-16</t>
+          <t>7.5648e-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3186,14 +3187,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.3563e-14</t>
+          <t>2.3577e-14</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1269</v>
       </c>
       <c r="H10" t="n">
-        <v>0.22395</v>
+        <v>0.22364</v>
       </c>
     </row>
     <row r="11">
@@ -3207,29 +3208,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.1758e-01</t>
+          <t>2.1718e-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.6045e-15</t>
+          <t>5.1697e-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.0004e-01</t>
+          <t>2.0003e-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.3992e-13</t>
+          <t>6.4021e-13</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1269</v>
       </c>
       <c r="H11" t="n">
-        <v>0.21758</v>
+        <v>0.21718</v>
       </c>
     </row>
     <row r="12">
@@ -3243,12 +3244,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.1490e-01</t>
+          <t>2.1453e-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0063e-14</t>
+          <t>1.1194e-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3258,14 +3259,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.0739e-12</t>
+          <t>1.0743e-12</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1269</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2149</v>
+        <v>0.21453</v>
       </c>
     </row>
     <row r="13">
@@ -3279,12 +3280,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.1435e-01</t>
+          <t>2.1395e-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.1788e-14</t>
+          <t>1.3245e-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3294,14 +3295,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.0305e-12</t>
+          <t>2.0313e-12</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1269</v>
       </c>
       <c r="H13" t="n">
-        <v>0.21435</v>
+        <v>0.21395</v>
       </c>
     </row>
     <row r="14">
@@ -3315,29 +3316,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.1285e-01</t>
+          <t>2.1249e-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.8171e-14</t>
+          <t>2.0147e-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.9507e-01</t>
+          <t>1.9506e-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.3932e-12</t>
+          <t>2.3940e-12</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1269</v>
       </c>
       <c r="H14" t="n">
-        <v>0.21285</v>
+        <v>0.21249</v>
       </c>
     </row>
     <row r="15">
@@ -3351,29 +3352,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.0406e-01</t>
+          <t>2.0419e-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.1440e-13</t>
+          <t>2.0704e-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.1604e-01</t>
+          <t>2.1605e-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.2167e-15</t>
+          <t>7.2079e-15</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1269</v>
       </c>
       <c r="H15" t="n">
-        <v>0.20406</v>
+        <v>0.20419</v>
       </c>
     </row>
     <row r="16">
@@ -3387,12 +3388,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.0380e-01</t>
+          <t>2.0382e-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.3007e-13</t>
+          <t>2.2887e-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3402,14 +3403,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.3105e-15</t>
+          <t>1.3099e-15</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1269</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2038</v>
+        <v>0.20382</v>
       </c>
     </row>
     <row r="17">
@@ -3423,12 +3424,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.9951e-01</t>
+          <t>1.9947e-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.3758e-13</t>
+          <t>7.4535e-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3438,14 +3439,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3.6724e-15</t>
+          <t>3.6718e-15</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1269</v>
       </c>
       <c r="H17" t="n">
-        <v>0.19951</v>
+        <v>0.19947</v>
       </c>
     </row>
     <row r="18">
@@ -3459,12 +3460,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.4703e-01</t>
+          <t>1.4697e-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.4311e-07</t>
+          <t>1.4491e-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3474,14 +3475,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.7743e-14</t>
+          <t>2.7762e-14</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1269</v>
       </c>
       <c r="H18" t="n">
-        <v>0.14703</v>
+        <v>0.14697</v>
       </c>
     </row>
     <row r="19">
@@ -3495,12 +3496,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.4138e-01</t>
+          <t>1.4192e-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.2586e-07</t>
+          <t>3.8490e-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3510,14 +3511,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.8384e-10</t>
+          <t>1.8362e-10</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1269</v>
       </c>
       <c r="H19" t="n">
-        <v>0.14138</v>
+        <v>0.14192</v>
       </c>
     </row>
     <row r="20">
@@ -3531,29 +3532,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.2476e-01</t>
+          <t>-1.2574e-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3015e-06</t>
+          <t>7.0319e-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.3119e-01</t>
+          <t>-1.3120e-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.7426e-06</t>
+          <t>2.7417e-06</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.12476</v>
+        <v>0.12574</v>
       </c>
     </row>
     <row r="21">
@@ -3567,12 +3568,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.2317e-01</t>
+          <t>-1.2273e-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.0813e-05</t>
+          <t>1.1632e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3582,14 +3583,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5.3119e-11</t>
+          <t>5.3182e-11</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1269</v>
       </c>
       <c r="H21" t="n">
-        <v>0.12317</v>
+        <v>0.12273</v>
       </c>
     </row>
   </sheetData>
@@ -3603,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3626,11 +3627,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.68000000000001</v>
+        <v>1.272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3641,11 +3642,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.738</v>
+        <v>1.204</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3656,11 +3657,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.618</v>
+        <v>1.12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3671,11 +3672,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>skewness</t>
+          <t>slope_abs_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.362</v>
+        <v>1.097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3686,11 +3687,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>slope_abs_mean</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.109</v>
+        <v>1.05</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3701,28 +3702,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>PatientAge</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.056</v>
+        <v>1.05</v>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PatientAge</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
         </is>
@@ -3739,7 +3725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3762,11 +3748,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.68000000000001</v>
+        <v>1.272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3777,11 +3763,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.738</v>
+        <v>1.204</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3792,11 +3778,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.618</v>
+        <v>1.12</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3807,11 +3793,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>skewness</t>
+          <t>slope_abs_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.362</v>
+        <v>1.097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3822,11 +3808,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>slope_abs_mean</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.109</v>
+        <v>1.05</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3837,11 +3823,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>PatientAge</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.056</v>
+        <v>1.05</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3852,26 +3838,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PatientAge</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.05</v>
+        <v>1.272</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>현재 선택 (SELECTED_AEC_FEATURES)</t>
+          <t>mean 제외, AUC_normalized 포함</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.447</v>
+        <v>1.205</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3886,7 +3872,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.532</v>
+        <v>1.12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3897,11 +3883,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>slope_abs_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.632</v>
+        <v>1.097</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3912,11 +3898,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>skewness</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.356</v>
+        <v>1.05</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -3927,11 +3913,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>slope_abs_mean</t>
+          <t>PatientAge</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.108</v>
+        <v>1.05</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3942,43 +3928,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.056</v>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mean 제외, AUC_normalized 포함</t>
+          <t>AUC_normalized 제외, mean 포함</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PatientAge</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1.05</v>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mean 제외, AUC_normalized 포함</t>
+          <t>AUC_normalized 제외, mean 포함</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.272</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -3989,13 +3977,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>slope_abs_mean</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.204</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -4006,11 +3992,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>66.68000000000001</v>
+        <v>1.097</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -4021,11 +4007,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.618</v>
+        <v>1.05</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -4036,11 +4022,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>skewness</t>
+          <t>PatientAge</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.362</v>
+        <v>1.05</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -4051,56 +4037,56 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>slope_abs_mean</t>
+          <t>AUC_normalized</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.109</v>
+        <v>51161.094</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUC_normalized 제외, mean 포함</t>
+          <t>mean + AUC_normalized 둘 다 포함</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.056</v>
+        <v>51152.687</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AUC_normalized 제외, mean 포함</t>
+          <t>mean + AUC_normalized 둘 다 포함</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PatientAge</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.05</v>
+        <v>1.329</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AUC_normalized 제외, mean 포함</t>
+          <t>mean + AUC_normalized 둘 다 포함</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>51391.103</v>
+        <v>1.248</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4111,11 +4097,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AUC_normalized</t>
+          <t>slope_abs_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>51219.635</v>
+        <v>1.111</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4126,11 +4112,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>PatientAge</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>66.756</v>
+        <v>1.066</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4141,73 +4127,13 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.658</v>
+        <v>1.063</v>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>mean + AUC_normalized 둘 다 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>skewness</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1.412</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>mean + AUC_normalized 둘 다 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>slope_abs_mean</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1.124</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>mean + AUC_normalized 둘 다 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1.071</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>mean + AUC_normalized 둘 다 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>PatientAge</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>mean + AUC_normalized 둘 다 포함</t>
         </is>
@@ -4224,138 +4150,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PatientAge</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>P25</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>P75</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>P33</t>
+          <t>slope_abs_mean</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>M</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>PatientAge</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>637</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>147.92</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>26.92</v>
+        <v>0.0232</v>
       </c>
       <c r="E2" t="n">
+        <v>-0.2107</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.06710000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.0086</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Sex</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.08309999999999999</v>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
-        <v>131</v>
-      </c>
-      <c r="G2" t="n">
-        <v>147</v>
-      </c>
-      <c r="H2" t="n">
-        <v>165</v>
-      </c>
-      <c r="I2" t="n">
-        <v>279</v>
-      </c>
-      <c r="J2" t="n">
-        <v>116.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>632</v>
-      </c>
-      <c r="C3" t="n">
-        <v>104.33</v>
-      </c>
       <c r="D3" t="n">
-        <v>15.46</v>
+        <v>0.1186</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>-0.1679</v>
       </c>
       <c r="F3" t="n">
-        <v>95</v>
+        <v>-0.0871</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
-      </c>
-      <c r="H3" t="n">
-        <v>114</v>
-      </c>
-      <c r="I3" t="n">
-        <v>158</v>
-      </c>
-      <c r="J3" t="n">
-        <v>87</v>
-      </c>
-      <c r="K3" t="n">
-        <v>98</v>
+        <v>0.06759999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1186</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.1011</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.2355</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1982</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.2107</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.1679</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1011</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>skewness</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.06710000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0871</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2355</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0325</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>slope_abs_mean</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4369,13 +4346,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Sex</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -4385,606 +4362,122 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pct</t>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P33</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iCT 256</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>278</v>
+        <v>637</v>
       </c>
       <c r="C2" t="n">
-        <v>21.9</v>
+        <v>148</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2" t="n">
+        <v>131</v>
+      </c>
+      <c r="G2" t="n">
+        <v>147</v>
+      </c>
+      <c r="H2" t="n">
+        <v>165</v>
+      </c>
+      <c r="I2" t="n">
+        <v>279</v>
+      </c>
+      <c r="J2" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SOMATOM Definition Flash</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>271</v>
+        <v>632</v>
       </c>
       <c r="C3" t="n">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SOMATOM Definition AS+</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>202</v>
-      </c>
-      <c r="C4" t="n">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SOMATOM Force</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>177</v>
-      </c>
-      <c r="C5" t="n">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Revolution EVO</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sensation 64</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>61</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LightSpeed VCT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>48</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Discovery CT750 HD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>25</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Revolution CT</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>20</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Brilliance 64</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>13</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Aquilion ONE</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Aquilion</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SOMATOM Perspective</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ingenuity Core 128</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Aquilion PRIME</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Optima CT660</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>6</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Ingenuity CT</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sensation Open</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SOMATOM Definition Edge</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Ingenuity Core</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Ingenuity CT Elite</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SOMATOM Scope</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SOMATOM Definition</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SOMATOM Definition AS</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Aquilion/LB</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Alexion</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Brivo CT385 Series</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Spirit</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Activion16</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Supria</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Brilliance 40</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Aquilion Lightning</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Revolution HD</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sensation 16</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SOMATOM Emotion 16</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ECLOS</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>GMS Revolution FT</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Emotion 16</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>iCT SP</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SOMATOM go.Top</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Definition Edge</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MX 16</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Emotion 16 (2007)</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SOMATOM Drive</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Revolution Frontier</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.1</v>
+        <v>104.33</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F3" t="n">
+        <v>95</v>
+      </c>
+      <c r="G3" t="n">
+        <v>103</v>
+      </c>
+      <c r="H3" t="n">
+        <v>114</v>
+      </c>
+      <c r="I3" t="n">
+        <v>158</v>
+      </c>
+      <c r="J3" t="n">
+        <v>87</v>
+      </c>
+      <c r="K3" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -4998,6 +4491,635 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>iCT 256</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>278</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition Flash</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>271</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition AS+</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>202</v>
+      </c>
+      <c r="C4" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SOMATOM Force</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>177</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Revolution EVO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sensation 64</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LightSpeed VCT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>48</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Discovery CT750 HD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Revolution CT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brilliance 64</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aquilion ONE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aquilion</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SOMATOM Perspective</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ingenuity Core 128</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Optima CT660</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aquilion PRIME</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ingenuity CT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sensation Open</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition Edge</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ingenuity CT Elite</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SOMATOM Scope</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ingenuity Core</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Brivo CT385 Series</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alexion</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SOMATOM Definition AS</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Aquilion/LB</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spirit</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Revolution Frontier</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Activion16</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brilliance 40</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Definition Edge</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ECLOS</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>iCT SP</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Supria</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SOMATOM Drive</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Aquilion Lightning</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sensation 16</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SOMATOM go.Top</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Revolution HD</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MX 16</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Emotion 16 (2007)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Emotion 16</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SOMATOM Emotion 16</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GMS Revolution FT</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
